--- a/RiskUnit/reports/risk_hesabati_analitik.xlsx
+++ b/RiskUnit/reports/risk_hesabati_analitik.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1900,7 +1900,7 @@
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brent 2027–2030: 45 USD/barel</t>
+          <t>Brent 2026-nın qalan ayları (IV rüb) və 2027–2030: 45 USD/barel</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1971,10 +1971,10 @@
         <v>2026</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1779321468687796</v>
+        <v>-0.1762884481545175</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1779321468687796</v>
+        <v>-0.1762884481545175</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brent 2027–2030: 45 USD/barel</t>
+          <t>Brent 2026-nın qalan ayları (IV rüb) və 2027–2030: 45 USD/barel</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2005,13 +2005,13 @@
         <v>2027</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.317426464248032</v>
+        <v>-1.304406049406257</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9815693205438034</v>
+        <v>-0.9729543415631277</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3358571437042288</v>
+        <v>0.3314517078431294</v>
       </c>
     </row>
     <row r="4">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brent 2027–2030: 45 USD/barel</t>
+          <t>Brent 2026-nın qalan ayları (IV rüb) və 2027–2030: 45 USD/barel</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2039,13 +2039,13 @@
         <v>2028</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.050307418201153</v>
+        <v>-1.041058551635262</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3527354782916685</v>
+        <v>0.3492317310487962</v>
       </c>
       <c r="H4" t="n">
-        <v>1.403042896492821</v>
+        <v>1.390290282684059</v>
       </c>
     </row>
     <row r="5">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brent 2027–2030: 45 USD/barel</t>
+          <t>Brent 2026-nın qalan ayları (IV rüb) və 2027–2030: 45 USD/barel</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2073,13 +2073,13 @@
         <v>2029</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.279391981197838</v>
+        <v>-0.2769392195947109</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.07646213555915526</v>
+        <v>-0.07607503433203533</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2029298456386828</v>
+        <v>0.2008641852626756</v>
       </c>
     </row>
     <row r="6">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brent 2027–2030: 45 USD/barel</t>
+          <t>Brent 2026-nın qalan ayları (IV rüb) və 2027–2030: 45 USD/barel</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2107,13 +2107,13 @@
         <v>2030</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1634807279921073</v>
+        <v>-0.161985593542215</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0359552058333259</v>
+        <v>-0.03582079671119587</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1275255221587814</v>
+        <v>0.1261647968310191</v>
       </c>
     </row>
     <row r="7">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brent 2027–2030: 45 USD/barel</t>
+          <t>Brent 2026-nın qalan ayları (IV rüb) və 2027–2030: 45 USD/barel</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2141,13 +2141,13 @@
         <v>2026</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6346723516226636</v>
+        <v>-0.6330234821093823</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6354997637792668</v>
+        <v>-0.6337126894477443</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0008274121566032022</v>
+        <v>-0.0006892073383619746</v>
       </c>
     </row>
     <row r="8">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brent 2027–2030: 45 USD/barel</t>
+          <t>Brent 2026-nın qalan ayları (IV rüb) və 2027–2030: 45 USD/barel</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2175,13 +2175,13 @@
         <v>2027</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.586176905747503</v>
+        <v>-3.574295596750548</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.423920864307219</v>
+        <v>-3.414074692832784</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1622560414402834</v>
+        <v>0.160220903917764</v>
       </c>
     </row>
     <row r="9">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brent 2027–2030: 45 USD/barel</t>
+          <t>Brent 2026-nın qalan ayları (IV rüb) və 2027–2030: 45 USD/barel</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2209,13 +2209,13 @@
         <v>2028</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.791730273184152</v>
+        <v>-1.782369599686628</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.363348564960593</v>
+        <v>-1.36440959527873</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4283817082235588</v>
+        <v>0.4179600044078988</v>
       </c>
     </row>
     <row r="10">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brent 2027–2030: 45 USD/barel</t>
+          <t>Brent 2026-nın qalan ayları (IV rüb) və 2027–2030: 45 USD/barel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2243,13 +2243,13 @@
         <v>2029</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1258111091127079</v>
+        <v>-0.122987257247031</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.05847520647763105</v>
+        <v>-0.05773153629891858</v>
       </c>
       <c r="H10" t="n">
-        <v>0.06733590263507683</v>
+        <v>0.06525572094811238</v>
       </c>
     </row>
     <row r="11">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brent 2027–2030: 45 USD/barel</t>
+          <t>Brent 2026-nın qalan ayları (IV rüb) və 2027–2030: 45 USD/barel</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2277,13 +2277,13 @@
         <v>2030</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.02794703461860149</v>
+        <v>-0.02621753511010549</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01475603963534233</v>
+        <v>0.01507129029475518</v>
       </c>
       <c r="H11" t="n">
-        <v>0.04270307425394382</v>
+        <v>0.04128882540486067</v>
       </c>
     </row>
     <row r="12">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brent 2027–2030: 45 USD/barel</t>
+          <t>Brent 2026-nın qalan ayları (IV rüb) və 2027–2030: 45 USD/barel</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2311,10 +2311,10 @@
         <v>2026</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.08151090827130159</v>
+        <v>-0.08130732574825661</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.08151090827130159</v>
+        <v>-0.08130732574825661</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brent 2027–2030: 45 USD/barel</t>
+          <t>Brent 2026-nın qalan ayları (IV rüb) və 2027–2030: 45 USD/barel</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2345,13 +2345,13 @@
         <v>2027</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2804440723855136</v>
+        <v>-0.2766079203164108</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7532379385012371</v>
+        <v>-0.7483947687556116</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4727938661157235</v>
+        <v>-0.4717868484392008</v>
       </c>
     </row>
     <row r="14">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brent 2027–2030: 45 USD/barel</t>
+          <t>Brent 2026-nın qalan ayları (IV rüb) və 2027–2030: 45 USD/barel</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2379,13 +2379,13 @@
         <v>2028</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1846460792726903</v>
+        <v>-0.1703470590522539</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.540070732733791</v>
+        <v>-2.517825315701139</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.355424653461101</v>
+        <v>-2.347478256648885</v>
       </c>
     </row>
     <row r="15">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brent 2027–2030: 45 USD/barel</t>
+          <t>Brent 2026-nın qalan ayları (IV rüb) və 2027–2030: 45 USD/barel</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2413,13 +2413,13 @@
         <v>2029</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.09974184886796118</v>
+        <v>-0.08262987022288822</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.485621719261452</v>
+        <v>-2.419752246575483</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.385879870393491</v>
+        <v>-2.337122376352594</v>
       </c>
     </row>
     <row r="16">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brent 2027–2030: 45 USD/barel</t>
+          <t>Brent 2026-nın qalan ayları (IV rüb) və 2027–2030: 45 USD/barel</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2447,13 +2447,13 @@
         <v>2030</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0615340204442912</v>
+        <v>-0.0426403600256772</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.46294574215794</v>
+        <v>-2.399445453370543</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.401411721713649</v>
+        <v>-2.356805093344866</v>
       </c>
     </row>
     <row r="17">
@@ -2515,13 +2515,13 @@
         <v>2027</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.41196959861366</v>
+        <v>-0.4083217685019971</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4119695986136591</v>
+        <v>-0.4083217685019971</v>
       </c>
       <c r="H18" t="n">
-        <v>8.881784197001252e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2549,10 +2549,10 @@
         <v>2028</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2091522356927591</v>
+        <v>-0.2076317023914989</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2091522356927591</v>
+        <v>-0.2076317023914989</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2583,13 +2583,13 @@
         <v>2029</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.009268003227918875</v>
+        <v>-0.00950878492972862</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.009268003227918875</v>
+        <v>-0.009508784929730396</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
     </row>
     <row r="21">
@@ -2617,13 +2617,13 @@
         <v>2030</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.01266821071749291</v>
+        <v>-0.01269385220867392</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0126682107174938</v>
+        <v>-0.01269385220867392</v>
       </c>
       <c r="H21" t="n">
-        <v>-8.881784197001252e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2685,10 +2685,10 @@
         <v>2027</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1402085588454067</v>
+        <v>-0.1360676496041862</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1402085588454067</v>
+        <v>-0.1360676496041862</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2719,10 +2719,10 @@
         <v>2028</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.07117490957550032</v>
+        <v>-0.06918221275448833</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.07117490957550032</v>
+        <v>-0.06918221275448833</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2753,13 +2753,13 @@
         <v>2029</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.003137616319508929</v>
+        <v>-0.003149556338235548</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.003137616319508929</v>
+        <v>-0.00314955633823466</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>8.881784197001252e-16</v>
       </c>
     </row>
     <row r="26">
@@ -2787,13 +2787,13 @@
         <v>2030</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.004290721885238824</v>
+        <v>-0.004205880213074664</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.004290721885238824</v>
+        <v>-0.004205880213076441</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
     </row>
     <row r="27">
@@ -2855,10 +2855,10 @@
         <v>2027</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.03233307657421591</v>
+        <v>-0.03181933433594147</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.03233307657421591</v>
+        <v>-0.03181933433594147</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>2028</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0515610715638186</v>
+        <v>-0.04972431061114868</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0515610715638186</v>
+        <v>-0.04972431061114868</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2923,10 +2923,10 @@
         <v>2029</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.05656464701197214</v>
+        <v>-0.05411310554297213</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.05656464701197214</v>
+        <v>-0.05411310554297213</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -2957,10 +2957,10 @@
         <v>2030</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.06207172310794075</v>
+        <v>-0.0594462444650793</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.06207172310794075</v>
+        <v>-0.0594462444650793</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>S1 + 2027-də 25% devalvasiya (vahid məzənnə modulu)</t>
+          <t>S1 (Brent 2026 IV rüb – 2030: 45 USD) + 2027-də 25% devalvasiya (vahid məzənnə modulu: İQİ, qeyri-neft, büdcə, borc)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2991,10 +2991,10 @@
         <v>2026</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1779321468687796</v>
+        <v>-0.1762884481545175</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.1779321468687796</v>
+        <v>-0.1762884481545175</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>S1 + 2027-də 25% devalvasiya (vahid məzənnə modulu)</t>
+          <t>S1 (Brent 2026 IV rüb – 2030: 45 USD) + 2027-də 25% devalvasiya (vahid məzənnə modulu: İQİ, qeyri-neft, büdcə, borc)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3025,13 +3025,13 @@
         <v>2027</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.528019714468813</v>
+        <v>-1.526972504807834</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.173583083986359</v>
+        <v>-1.175461284298988</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3544366304824544</v>
+        <v>0.3515112205088462</v>
       </c>
     </row>
     <row r="34">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>S1 + 2027-də 25% devalvasiya (vahid məzənnə modulu)</t>
+          <t>S1 (Brent 2026 IV rüb – 2030: 45 USD) + 2027-də 25% devalvasiya (vahid məzənnə modulu: İQİ, qeyri-neft, büdcə, borc)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3059,13 +3059,13 @@
         <v>2028</v>
       </c>
       <c r="F34" t="n">
-        <v>-3.595723411052398</v>
+        <v>-3.59294636717389</v>
       </c>
       <c r="G34" t="n">
-        <v>-2.271375779093899</v>
+        <v>-2.281005175698831</v>
       </c>
       <c r="H34" t="n">
-        <v>1.324347631958499</v>
+        <v>1.311941191475058</v>
       </c>
     </row>
     <row r="35">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>S1 + 2027-də 25% devalvasiya (vahid məzənnə modulu)</t>
+          <t>S1 (Brent 2026 IV rüb – 2030: 45 USD) + 2027-də 25% devalvasiya (vahid məzənnə modulu: İQİ, qeyri-neft, büdcə, borc)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3093,13 +3093,13 @@
         <v>2029</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.279391981197838</v>
+        <v>-0.2769392195947109</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.07646213555915526</v>
+        <v>-0.07607503433203533</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2029298456386828</v>
+        <v>0.2008641852626756</v>
       </c>
     </row>
     <row r="36">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>S1 + 2027-də 25% devalvasiya (vahid məzənnə modulu)</t>
+          <t>S1 (Brent 2026 IV rüb – 2030: 45 USD) + 2027-də 25% devalvasiya (vahid məzənnə modulu: İQİ, qeyri-neft, büdcə, borc)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3127,13 +3127,13 @@
         <v>2030</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.1634807279921073</v>
+        <v>-0.161985593542215</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0359552058333259</v>
+        <v>-0.03582079671119587</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1275255221587814</v>
+        <v>0.1261647968310191</v>
       </c>
     </row>
     <row r="37">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>S1 + 2027-də 25% devalvasiya (vahid məzənnə modulu)</t>
+          <t>S1 (Brent 2026 IV rüb – 2030: 45 USD) + 2027-də 25% devalvasiya (vahid məzənnə modulu: İQİ, qeyri-neft, büdcə, borc)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3161,13 +3161,13 @@
         <v>2026</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6346723516226636</v>
+        <v>-0.6330234821093823</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.6354997637792668</v>
+        <v>-0.6337126894477443</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.0008274121566032022</v>
+        <v>-0.0006892073383619746</v>
       </c>
     </row>
     <row r="38">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>S1 + 2027-də 25% devalvasiya (vahid məzənnə modulu)</t>
+          <t>S1 (Brent 2026 IV rüb – 2030: 45 USD) + 2027-də 25% devalvasiya (vahid məzənnə modulu: İQİ, qeyri-neft, büdcə, borc)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3195,13 +3195,13 @@
         <v>2027</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9719722083656972</v>
+        <v>0.9860279662581037</v>
       </c>
       <c r="G38" t="n">
-        <v>1.147155369391083</v>
+        <v>1.154204737379221</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1751831610253856</v>
+        <v>0.1681767711211171</v>
       </c>
     </row>
     <row r="39">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>S1 + 2027-də 25% devalvasiya (vahid məzənnə modulu)</t>
+          <t>S1 (Brent 2026 IV rüb – 2030: 45 USD) + 2027-də 25% devalvasiya (vahid məzənnə modulu: İQİ, qeyri-neft, büdcə, borc)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3229,13 +3229,13 @@
         <v>2028</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3754507245071226</v>
+        <v>0.3868902346731344</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8103261939600017</v>
+        <v>0.8082634409569565</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4348754694528791</v>
+        <v>0.421373206283822</v>
       </c>
     </row>
     <row r="40">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>S1 + 2027-də 25% devalvasiya (vahid məzənnə modulu)</t>
+          <t>S1 (Brent 2026 IV rüb – 2030: 45 USD) + 2027-də 25% devalvasiya (vahid məzənnə modulu: İQİ, qeyri-neft, büdcə, borc)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3263,13 +3263,13 @@
         <v>2029</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.1258111091127079</v>
+        <v>-0.122987257247031</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.05847520647763105</v>
+        <v>-0.05773153629891858</v>
       </c>
       <c r="H40" t="n">
-        <v>0.06733590263507683</v>
+        <v>0.06525572094811238</v>
       </c>
     </row>
     <row r="41">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>S1 + 2027-də 25% devalvasiya (vahid məzənnə modulu)</t>
+          <t>S1 (Brent 2026 IV rüb – 2030: 45 USD) + 2027-də 25% devalvasiya (vahid məzənnə modulu: İQİ, qeyri-neft, büdcə, borc)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3297,13 +3297,13 @@
         <v>2030</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.02794703461860149</v>
+        <v>-0.02621753511010549</v>
       </c>
       <c r="G41" t="n">
-        <v>0.01475603963534233</v>
+        <v>0.01507129029475518</v>
       </c>
       <c r="H41" t="n">
-        <v>0.04270307425394382</v>
+        <v>0.04128882540486067</v>
       </c>
     </row>
     <row r="42">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>S1 + 2027-də 25% devalvasiya (vahid məzənnə modulu)</t>
+          <t>S1 (Brent 2026 IV rüb – 2030: 45 USD) + 2027-də 25% devalvasiya (vahid məzənnə modulu: İQİ, qeyri-neft, büdcə, borc)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3331,10 +3331,10 @@
         <v>2026</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.08151090827130159</v>
+        <v>-0.08130732574825661</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.08151090827130159</v>
+        <v>-0.08130732574825661</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>S1 + 2027-də 25% devalvasiya (vahid məzənnə modulu)</t>
+          <t>S1 (Brent 2026 IV rüb – 2030: 45 USD) + 2027-də 25% devalvasiya (vahid məzənnə modulu: İQİ, qeyri-neft, büdcə, borc)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3365,13 +3365,13 @@
         <v>2027</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.2804440723855136</v>
+        <v>-0.3161509953688227</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.7532379385012371</v>
+        <v>-0.7879378438080236</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.4727938661157235</v>
+        <v>-0.4717868484392008</v>
       </c>
     </row>
     <row r="44">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>S1 + 2027-də 25% devalvasiya (vahid məzənnə modulu)</t>
+          <t>S1 (Brent 2026 IV rüb – 2030: 45 USD) + 2027-də 25% devalvasiya (vahid məzənnə modulu: İQİ, qeyri-neft, büdcə, borc)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3399,13 +3399,13 @@
         <v>2028</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.1846460792726903</v>
+        <v>-0.3246339371617754</v>
       </c>
       <c r="G44" t="n">
-        <v>-2.540070732733791</v>
+        <v>-2.672112193810661</v>
       </c>
       <c r="H44" t="n">
-        <v>-2.355424653461101</v>
+        <v>-2.347478256648885</v>
       </c>
     </row>
     <row r="45">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>S1 + 2027-də 25% devalvasiya (vahid məzənnə modulu)</t>
+          <t>S1 (Brent 2026 IV rüb – 2030: 45 USD) + 2027-də 25% devalvasiya (vahid məzənnə modulu: İQİ, qeyri-neft, büdcə, borc)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3433,13 +3433,13 @@
         <v>2029</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.09974184886796118</v>
+        <v>-0.3186531305966057</v>
       </c>
       <c r="G45" t="n">
-        <v>-2.485621719261452</v>
+        <v>-2.6557755069492</v>
       </c>
       <c r="H45" t="n">
-        <v>-2.385879870393491</v>
+        <v>-2.337122376352594</v>
       </c>
     </row>
     <row r="46">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>S1 + 2027-də 25% devalvasiya (vahid məzənnə modulu)</t>
+          <t>S1 (Brent 2026 IV rüb – 2030: 45 USD) + 2027-də 25% devalvasiya (vahid məzənnə modulu: İQİ, qeyri-neft, büdcə, borc)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3467,13 +3467,13 @@
         <v>2030</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.0615340204442912</v>
+        <v>-0.305545537759454</v>
       </c>
       <c r="G46" t="n">
-        <v>-2.46294574215794</v>
+        <v>-2.66235063110432</v>
       </c>
       <c r="H46" t="n">
-        <v>-2.401411721713649</v>
+        <v>-2.356805093344866</v>
       </c>
     </row>
     <row r="47">
@@ -3535,10 +3535,10 @@
         <v>2027</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.9591938170928263</v>
+        <v>-0.9554788675466384</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.9591938170928263</v>
+        <v>-0.9554788675466384</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -3569,10 +3569,10 @@
         <v>2028</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1435178401061634</v>
+        <v>0.1429799769128008</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1435178401061643</v>
+        <v>0.1429799769128017</v>
       </c>
       <c r="H49" t="n">
         <v>8.881784197001252e-16</v>
@@ -3603,13 +3603,13 @@
         <v>2029</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.006413764212247486</v>
+        <v>-0.006965888058394043</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.006413764212247486</v>
+        <v>-0.006965888058395819</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
     </row>
     <row r="51">
@@ -3637,13 +3637,13 @@
         <v>2030</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.006277482625684172</v>
+        <v>-0.006495684293906123</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.00627748262568506</v>
+        <v>-0.006495684293905235</v>
       </c>
       <c r="H51" t="n">
-        <v>-8.881784197001252e-16</v>
+        <v>8.881784197001252e-16</v>
       </c>
     </row>
     <row r="52">
@@ -3705,10 +3705,10 @@
         <v>2027</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1425443166511524</v>
+        <v>-0.1383200958852306</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.1425443166511524</v>
+        <v>-0.1383200958852306</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -3739,10 +3739,10 @@
         <v>2028</v>
       </c>
       <c r="F54" t="n">
-        <v>0.04913804519454246</v>
+        <v>0.04792293192886721</v>
       </c>
       <c r="G54" t="n">
-        <v>0.04913804519454246</v>
+        <v>0.04792293192886721</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -3773,10 +3773,10 @@
         <v>2029</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.002175256141994097</v>
+        <v>-0.002312702247595944</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.002175256141993209</v>
+        <v>-0.002312702247595055</v>
       </c>
       <c r="H55" t="n">
         <v>8.881784197001252e-16</v>
@@ -3807,13 +3807,13 @@
         <v>2030</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.002127669987725511</v>
+        <v>-0.002154457037382151</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.002127669987725511</v>
+        <v>-0.00215445703738304</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>-8.881784197001252e-16</v>
       </c>
     </row>
     <row r="57">
@@ -3875,10 +3875,10 @@
         <v>2027</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.04498220607440662</v>
+        <v>-0.0444781314056599</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.04498220607440662</v>
+        <v>-0.0444781314056599</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -3909,10 +3909,10 @@
         <v>2028</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.02837427181226834</v>
+        <v>-0.02642093607117313</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.02837427181226834</v>
+        <v>-0.02642093607117313</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3943,10 +3943,10 @@
         <v>2029</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.0306329066975739</v>
+        <v>-0.02928043109415783</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.0306329066975739</v>
+        <v>-0.02928043109415783</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3977,10 +3977,10 @@
         <v>2030</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.03338275372274227</v>
+        <v>-0.03199560000396093</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.03338275372274227</v>
+        <v>-0.03199560000396093</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -4045,10 +4045,10 @@
         <v>2027</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.7315376425034241</v>
+        <v>-0.7348075070450051</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.7315376425034241</v>
+        <v>-0.7348075070450051</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -4079,10 +4079,10 @@
         <v>2028</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6656049172189604</v>
+        <v>0.6610227230764156</v>
       </c>
       <c r="G64" t="n">
-        <v>0.6656049172189604</v>
+        <v>0.6610227230764156</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -4113,10 +4113,10 @@
         <v>2029</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2854365206756455</v>
+        <v>0.2878986903811587</v>
       </c>
       <c r="G65" t="n">
-        <v>0.2854365206756455</v>
+        <v>0.2878986903811587</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -4147,13 +4147,13 @@
         <v>2030</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.1015234126422904</v>
+        <v>-0.09752811284205265</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.1015234126422904</v>
+        <v>-0.09752811284205176</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>8.881784197001252e-16</v>
       </c>
     </row>
     <row r="67">
@@ -4215,10 +4215,10 @@
         <v>2027</v>
       </c>
       <c r="F68" t="n">
-        <v>0.108265245731122</v>
+        <v>0.1049055308156017</v>
       </c>
       <c r="G68" t="n">
-        <v>0.108265245731122</v>
+        <v>0.1049055308156017</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -4249,10 +4249,10 @@
         <v>2028</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1375433921228613</v>
+        <v>0.1331303981616285</v>
       </c>
       <c r="G69" t="n">
-        <v>0.1375433921228613</v>
+        <v>0.1331303981616285</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -4283,10 +4283,10 @@
         <v>2029</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.08165335299745191</v>
+        <v>-0.0791288293975434</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.08165335299745102</v>
+        <v>-0.07912882939754251</v>
       </c>
       <c r="H70" t="n">
         <v>8.881784197001252e-16</v>
@@ -4317,13 +4317,13 @@
         <v>2030</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.1240942126341649</v>
+        <v>-0.1201708205713574</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.1240942126341649</v>
+        <v>-0.1201708205713583</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>-8.881784197001252e-16</v>
       </c>
     </row>
     <row r="72">
@@ -4385,10 +4385,10 @@
         <v>2027</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.4615964231143015</v>
+        <v>-0.4619770556446373</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.4615964231143015</v>
+        <v>-0.4619770556446373</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -4419,10 +4419,10 @@
         <v>2028</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.9686669286773568</v>
+        <v>-0.9583461762138585</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.9686669286773568</v>
+        <v>-0.9583461762138585</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -4453,10 +4453,10 @@
         <v>2029</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.5924704444828193</v>
+        <v>-0.5713491242606209</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.5924704444828193</v>
+        <v>-0.5713491242606209</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -4487,10 +4487,10 @@
         <v>2030</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.1686579902628476</v>
+        <v>-0.1581394646525698</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.1686579902628476</v>
+        <v>-0.1581394646525698</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -4555,13 +4555,13 @@
         <v>2027</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.1753617142078276</v>
+        <v>-0.1736135842269633</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.1691808232548873</v>
+        <v>-0.1675429244510198</v>
       </c>
       <c r="H78" t="n">
-        <v>0.006180890952940388</v>
+        <v>0.006070659775943454</v>
       </c>
     </row>
     <row r="79">
@@ -4589,13 +4589,13 @@
         <v>2028</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.3134661268071639</v>
+        <v>-0.3105232240505558</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.02489042424656596</v>
+        <v>-0.02487126408207985</v>
       </c>
       <c r="H79" t="n">
-        <v>0.2885757025605979</v>
+        <v>0.2856519599684759</v>
       </c>
     </row>
     <row r="80">
@@ -4623,13 +4623,13 @@
         <v>2029</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.3431941572265078</v>
+        <v>-0.3400000097013987</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.1054544461129394</v>
+        <v>-0.1046233635218101</v>
       </c>
       <c r="H80" t="n">
-        <v>0.2377397111135684</v>
+        <v>0.2353766461795885</v>
       </c>
     </row>
     <row r="81">
@@ -4657,13 +4657,13 @@
         <v>2030</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.3592028506579812</v>
+        <v>-0.3558670213688684</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.1077140786222097</v>
+        <v>-0.1068821053574558</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2514887720357715</v>
+        <v>0.2489849160114126</v>
       </c>
     </row>
     <row r="82">
@@ -4725,13 +4725,13 @@
         <v>2027</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.4741908069922971</v>
+        <v>-0.4704081038247612</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.4721374003572603</v>
+        <v>-0.4702218106418945</v>
       </c>
       <c r="H83" t="n">
-        <v>0.002053406635036836</v>
+        <v>0.0001862931828666703</v>
       </c>
     </row>
     <row r="84">
@@ -4759,13 +4759,13 @@
         <v>2028</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.7143220229312135</v>
+        <v>-0.7117866545319611</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.6182355791619951</v>
+        <v>-0.6185918610833969</v>
       </c>
       <c r="H84" t="n">
-        <v>0.09608644376921838</v>
+        <v>0.09319479344856418</v>
       </c>
     </row>
     <row r="85">
@@ -4793,13 +4793,13 @@
         <v>2029</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.7284544454535444</v>
+        <v>-0.724695079101906</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.6462879647371782</v>
+        <v>-0.6452185198854732</v>
       </c>
       <c r="H85" t="n">
-        <v>0.08216648071636623</v>
+        <v>0.07947655921643282</v>
       </c>
     </row>
     <row r="86">
@@ -4827,13 +4827,13 @@
         <v>2030</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.7341571834880272</v>
+        <v>-0.7301276744727518</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.6468683240462862</v>
+        <v>-0.6458518982624657</v>
       </c>
       <c r="H86" t="n">
-        <v>0.08728885944174092</v>
+        <v>0.08427577621028615</v>
       </c>
     </row>
     <row r="87">
@@ -4895,10 +4895,10 @@
         <v>2027</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.04336769518172867</v>
+        <v>-0.04331803105131488</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.04336769518172867</v>
+        <v>-0.04331803105131488</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4929,13 +4929,13 @@
         <v>2028</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.06781163791150771</v>
+        <v>-0.06589528380863141</v>
       </c>
       <c r="G89" t="n">
-        <v>-0.4543542261407181</v>
+        <v>-0.4530613926311304</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.3865425882292104</v>
+        <v>-0.387166108822499</v>
       </c>
     </row>
     <row r="90">
@@ -4963,13 +4963,13 @@
         <v>2029</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.07354737127334944</v>
+        <v>-0.0695718950674072</v>
       </c>
       <c r="G90" t="n">
-        <v>-0.7146379747373359</v>
+        <v>-0.7027292852036823</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.6410906034639865</v>
+        <v>-0.633157390136275</v>
       </c>
     </row>
     <row r="91">
@@ -4997,13 +4997,13 @@
         <v>2030</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.07385042839765105</v>
+        <v>-0.06778518490274274</v>
       </c>
       <c r="G91" t="n">
-        <v>-0.9501164746634755</v>
+        <v>-0.9315615555377069</v>
       </c>
       <c r="H91" t="n">
-        <v>-0.8762660462658245</v>
+        <v>-0.8637763706349642</v>
       </c>
     </row>
     <row r="92">
@@ -5065,13 +5065,13 @@
         <v>2027</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.1551905081419491</v>
+        <v>-0.1554323518774474</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.1528491073792715</v>
+        <v>-0.1527214122626237</v>
       </c>
       <c r="H93" t="n">
-        <v>0.002341400762677637</v>
+        <v>0.002710939614823715</v>
       </c>
     </row>
     <row r="94">
@@ -5099,13 +5099,13 @@
         <v>2028</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1463641980178423</v>
+        <v>0.146689498698219</v>
       </c>
       <c r="G94" t="n">
-        <v>0.1464171915442076</v>
+        <v>0.1467920952795234</v>
       </c>
       <c r="H94" t="n">
-        <v>5.299352636534138e-05</v>
+        <v>0.0001025965813044039</v>
       </c>
     </row>
     <row r="95">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Brent 2027: 60 USD, 2028–2030: makro baza yolu</t>
+          <t>Brent 2026 IV rüb və 2027: 60 USD, 2028–2030: makro baza yolu</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5541,10 +5541,10 @@
         <v>2026</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.06638997689290349</v>
+        <v>-0.06577709275576105</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.06638997689290349</v>
+        <v>-0.06577709275576105</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brent 2027: 60 USD, 2028–2030: makro baza yolu</t>
+          <t>Brent 2026 IV rüb və 2027: 60 USD, 2028–2030: makro baza yolu</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5575,13 +5575,13 @@
         <v>2027</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.4621870669752184</v>
+        <v>-0.4576488314617837</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.4548085008466796</v>
+        <v>-0.4503463200256199</v>
       </c>
       <c r="H108" t="n">
-        <v>0.007378566128538822</v>
+        <v>0.007302511436163783</v>
       </c>
     </row>
     <row r="109">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brent 2027: 60 USD, 2028–2030: makro baza yolu</t>
+          <t>Brent 2026 IV rüb və 2027: 60 USD, 2028–2030: makro baza yolu</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5609,13 +5609,13 @@
         <v>2028</v>
       </c>
       <c r="F109" t="n">
-        <v>0.1171824156381192</v>
+        <v>0.1156160572474603</v>
       </c>
       <c r="G109" t="n">
-        <v>0.4381387715416363</v>
+        <v>0.4337060284978893</v>
       </c>
       <c r="H109" t="n">
-        <v>0.3209563559035171</v>
+        <v>0.318089971250429</v>
       </c>
     </row>
     <row r="110">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brent 2027: 60 USD, 2028–2030: makro baza yolu</t>
+          <t>Brent 2026 IV rüb və 2027: 60 USD, 2028–2030: makro baza yolu</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5643,13 +5643,13 @@
         <v>2029</v>
       </c>
       <c r="F110" t="n">
-        <v>0.3010250749604593</v>
+        <v>0.2983847446253494</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0178820699202813</v>
+        <v>0.01774941227157889</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.283143005040178</v>
+        <v>-0.2806353323537705</v>
       </c>
     </row>
     <row r="111">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brent 2027: 60 USD, 2028–2030: makro baza yolu</t>
+          <t>Brent 2026 IV rüb və 2027: 60 USD, 2028–2030: makro baza yolu</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5677,13 +5677,13 @@
         <v>2030</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0377864913859165</v>
+        <v>0.03749707399040769</v>
       </c>
       <c r="G111" t="n">
-        <v>0.02623597036620051</v>
+        <v>0.02604713324793018</v>
       </c>
       <c r="H111" t="n">
-        <v>-0.01155052101971599</v>
+        <v>-0.01144994074247752</v>
       </c>
     </row>
     <row r="112">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brent 2027: 60 USD, 2028–2030: makro baza yolu</t>
+          <t>Brent 2026 IV rüb və 2027: 60 USD, 2028–2030: makro baza yolu</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5711,13 +5711,13 @@
         <v>2026</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.2328210380268736</v>
+        <v>-0.2322046592342719</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.2331240110510677</v>
+        <v>-0.232457025881212</v>
       </c>
       <c r="H112" t="n">
-        <v>-0.0003029730241941309</v>
+        <v>-0.0002523666469400609</v>
       </c>
     </row>
     <row r="113">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brent 2027: 60 USD, 2028–2030: makro baza yolu</t>
+          <t>Brent 2026 IV rüb və 2027: 60 USD, 2028–2030: makro baza yolu</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5745,13 +5745,13 @@
         <v>2027</v>
       </c>
       <c r="F113" t="n">
-        <v>-1.17049793033233</v>
+        <v>-1.1659014366787</v>
       </c>
       <c r="G113" t="n">
-        <v>-1.157321212593578</v>
+        <v>-1.152318135358208</v>
       </c>
       <c r="H113" t="n">
-        <v>0.01317671773875162</v>
+        <v>0.01358330132049179</v>
       </c>
     </row>
     <row r="114">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brent 2027: 60 USD, 2028–2030: makro baza yolu</t>
+          <t>Brent 2026 IV rüb və 2027: 60 USD, 2028–2030: makro baza yolu</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5779,13 +5779,13 @@
         <v>2028</v>
       </c>
       <c r="F114" t="n">
-        <v>0.7326111370892487</v>
+        <v>0.7294689197241846</v>
       </c>
       <c r="G114" t="n">
-        <v>0.8281937412029041</v>
+        <v>0.8238229389374192</v>
       </c>
       <c r="H114" t="n">
-        <v>0.09558260411365538</v>
+        <v>0.09435401921323461</v>
       </c>
     </row>
     <row r="115">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brent 2027: 60 USD, 2028–2030: makro baza yolu</t>
+          <t>Brent 2026 IV rüb və 2027: 60 USD, 2028–2030: makro baza yolu</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5813,13 +5813,13 @@
         <v>2029</v>
       </c>
       <c r="F115" t="n">
-        <v>0.6480738987812567</v>
+        <v>0.6457930701020187</v>
       </c>
       <c r="G115" t="n">
-        <v>0.5519387211053957</v>
+        <v>0.5518587292674138</v>
       </c>
       <c r="H115" t="n">
-        <v>-0.09613517767586099</v>
+        <v>-0.09393434083460495</v>
       </c>
     </row>
     <row r="116">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brent 2027: 60 USD, 2028–2030: makro baza yolu</t>
+          <t>Brent 2026 IV rüb və 2027: 60 USD, 2028–2030: makro baza yolu</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5847,13 +5847,13 @@
         <v>2030</v>
       </c>
       <c r="F116" t="n">
-        <v>0.01286891580519534</v>
+        <v>0.01250188724337775</v>
       </c>
       <c r="G116" t="n">
-        <v>0.008961373025909936</v>
+        <v>0.008704520326463516</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.0039075427792854</v>
+        <v>-0.003797366916914235</v>
       </c>
     </row>
     <row r="117">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brent 2027: 60 USD, 2028–2030: makro baza yolu</t>
+          <t>Brent 2026 IV rüb və 2027: 60 USD, 2028–2030: makro baza yolu</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5881,10 +5881,10 @@
         <v>2026</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.03052410159617558</v>
+        <v>-0.03044786427103197</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.03052410159617558</v>
+        <v>-0.03044786427103197</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brent 2027: 60 USD, 2028–2030: makro baza yolu</t>
+          <t>Brent 2026 IV rüb və 2027: 60 USD, 2028–2030: makro baza yolu</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5915,10 +5915,10 @@
         <v>2027</v>
       </c>
       <c r="F118" t="n">
-        <v>-0.104941676309245</v>
+        <v>-0.1035052090310428</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.104941676309245</v>
+        <v>-0.1035052090310428</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brent 2027: 60 USD, 2028–2030: makro baza yolu</t>
+          <t>Brent 2026 IV rüb və 2027: 60 USD, 2028–2030: makro baza yolu</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5949,13 +5949,13 @@
         <v>2028</v>
       </c>
       <c r="F119" t="n">
-        <v>0.03755279468532312</v>
+        <v>0.04284519356112003</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.4003100743353338</v>
+        <v>-0.3953857153193696</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.4378628690206569</v>
+        <v>-0.4382309088804896</v>
       </c>
     </row>
     <row r="120">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brent 2027: 60 USD, 2028–2030: makro baza yolu</t>
+          <t>Brent 2026 IV rüb və 2027: 60 USD, 2028–2030: makro baza yolu</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5983,13 +5983,13 @@
         <v>2029</v>
       </c>
       <c r="F120" t="n">
-        <v>0.03292292464977194</v>
+        <v>0.03477516692056408</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.01261187629897187</v>
+        <v>-0.0002834976430533855</v>
       </c>
       <c r="H120" t="n">
-        <v>-0.04553480094874381</v>
+        <v>-0.03505866456361746</v>
       </c>
     </row>
     <row r="121">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brent 2027: 60 USD, 2028–2030: makro baza yolu</t>
+          <t>Brent 2026 IV rüb və 2027: 60 USD, 2028–2030: makro baza yolu</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6017,13 +6017,13 @@
         <v>2030</v>
       </c>
       <c r="F121" t="n">
-        <v>0.01203530163256469</v>
+        <v>0.01346883776611498</v>
       </c>
       <c r="G121" t="n">
-        <v>-0.03036250578505517</v>
+        <v>-0.02920496824557368</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.04239780741761986</v>
+        <v>-0.04267380601168866</v>
       </c>
     </row>
   </sheetData>
@@ -6115,10 +6115,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.405954058235871</v>
+        <v>4.434965713136726</v>
       </c>
       <c r="E2" t="n">
-        <v>2.269466772527499</v>
+        <v>2.262182712487289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6127,11 +6127,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>P10 ilə median arasındakı 4.10 f.b. fərqi bağlamaq üçün; 1 mlrd AZN → qeyri-neft ÜDM +0.93% (FR1)</t>
+          <t>P10 ilə median arasındakı 4.09 f.b. fərqi bağlamaq üçün; 1 mlrd AZN → qeyri-neft ÜDM +0.92% (FR1)</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-8716.902602483498</v>
+        <v>-8781.535624787393</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -6156,10 +6156,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2859.231810936141</v>
+        <v>2878.080582204198</v>
       </c>
       <c r="E3" t="n">
-        <v>1472.764242228923</v>
+        <v>1468.048359184004</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>−200 b.p. → qeyri-neft ÜDM +0.29% (FR1); tələb olunan ölçü real faiz həddini aşa bilər</t>
+          <t>−200 b.p. → qeyri-neft ÜDM +0.28% (FR1); tələb olunan ölçü real faiz həddini aşa bilər</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1670911383057399</v>
+        <v>0.1577100195219112</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Brent enəndə dövlət investisiyası baza yolundan aşağı kəsilmirsə: P10 1.33% → 1.50%; ES10 -0.48% → -0.30%</t>
+          <t>Brent enəndə dövlət investisiyası baza yolundan aşağı kəsilmirsə: P10 1.34% → 1.50%; ES10 -0.47% → -0.30%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -8856,13 +8856,13 @@
         <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4745</v>
+        <v>0.47525</v>
       </c>
       <c r="E2" t="n">
         <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4745</v>
+        <v>0.47525</v>
       </c>
       <c r="G2" t="n">
         <v>12</v>
@@ -8910,13 +8910,13 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.141</v>
+        <v>0.1406</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>0.141</v>
+        <v>0.1406</v>
       </c>
       <c r="G4" t="n">
         <v>6</v>
@@ -9072,13 +9072,13 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0873</v>
+        <v>0.0963</v>
       </c>
       <c r="E10" t="n">
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0873</v>
+        <v>0.0963</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9516,7 +9516,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -9580,7 +9580,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9644,7 +9644,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9708,7 +9708,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -9772,7 +9772,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.652</v>
+        <v>0.7159</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -9903,12 +9903,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>korrelyasiya 0.82; epizodlar 2009/2015/2016/2020</t>
+          <t>korrelyasiya 0.76; epizodlar 2009/2015/2016/2020</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -9972,7 +9972,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -10172,7 +10172,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -10236,7 +10236,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -10368,7 +10368,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -10432,7 +10432,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -10512,7 +10512,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -10564,7 +10564,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -10628,7 +10628,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -10640,7 +10640,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -10760,7 +10760,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -10824,7 +10824,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -10888,7 +10888,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -10900,7 +10900,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -10952,7 +10952,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -11016,7 +11016,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -11080,7 +11080,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -11144,7 +11144,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -11208,7 +11208,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -11272,7 +11272,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -11336,7 +11336,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -11400,7 +11400,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -11464,7 +11464,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -11528,7 +11528,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -11596,7 +11596,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -11608,7 +11608,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -11744,7 +11744,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -11864,7 +11864,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -11925,12 +11925,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>nəticəsi açıqlanmış hədəf ili olan arxiv proqnozları ilk buraxılış rəqəmi ilə qiymətləndirilir; arxivdə 1 vintaj var — ilk yetişmə: 2026 faktiki (2027-ci ilin yazı)</t>
+          <t>nəticəsi açıqlanmış hədəf ili olan arxiv proqnozları ilk buraxılış rəqəmi ilə qiymətləndirilir; arxivdə 3 vintaj var — ilk yetişmə: 2026 faktiki (2027-ci ilin yazı)</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>etalon: 2 illik təsadüfi gəzinti xətası RMSE 1.00 f.b. / FR1 σ 3.49 f.b.</t>
+          <t>etalon: 2 illik təsadüfi gəzinti xətası RMSE 1.00 f.b. / FR1 σ 3.33 f.b.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>B-57b92d66be</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -12120,7 +12120,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -12162,7 +12162,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2852</v>
+        <v>0.2989</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>büdcə qalıq σ 0.29 dəfə miqyaslanır (FR1 σ 3.49 f.b. ≫ RW xətası 1.00 f.b.; əhatə 1.00)</t>
+          <t>büdcə qalıq σ 0.30 dəfə miqyaslanır (FR1 σ 3.33 f.b. ≫ RW xətası 1.00 f.b.; əhatə 1.00)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -12268,7 +12268,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -13850,22 +13850,22 @@
         <v>0.04</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4348</v>
+        <v>0.4306</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.3948</v>
+        <v>-0.3906</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2629</v>
+        <v>0.2606</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09288</v>
+        <v>0.092</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2314</v>
+        <v>0.2293</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1197</v>
+        <v>-0.1186</v>
       </c>
       <c r="I2" t="n">
         <v>-0.03264</v>
@@ -13891,22 +13891,22 @@
         <v>-1.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.187</v>
+        <v>0.1844</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.287</v>
+        <v>-1.284</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1807</v>
+        <v>0.1791</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1745</v>
+        <v>0.1729</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1029</v>
+        <v>0.102</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1817</v>
+        <v>-0.1801</v>
       </c>
       <c r="I3" t="n">
         <v>-0.08953999999999999</v>
@@ -13932,22 +13932,22 @@
         <v>3.88</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5073</v>
+        <v>0.5023</v>
       </c>
       <c r="D4" t="n">
-        <v>3.373</v>
+        <v>3.378</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6082</v>
+        <v>0.6028</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4267</v>
+        <v>0.4223</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4484</v>
+        <v>-0.4445</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.09055000000000001</v>
+        <v>-0.08974</v>
       </c>
       <c r="I4" t="n">
         <v>0.01134</v>
@@ -13973,22 +13973,22 @@
         <v>-8.52</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.962</v>
+        <v>-1.944</v>
       </c>
       <c r="D5" t="n">
-        <v>-6.558</v>
+        <v>-6.576</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8739</v>
+        <v>-0.8661</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.08123</v>
+        <v>-0.07917</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9722</v>
+        <v>-0.9636</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.03823</v>
+        <v>-0.03788</v>
       </c>
       <c r="I5" t="n">
         <v>0.003133</v>
@@ -14014,22 +14014,22 @@
         <v>-2.34</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08347</v>
+        <v>0.08235000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.423</v>
+        <v>-2.422</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4436</v>
+        <v>0.4397</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4423</v>
+        <v>-0.4389</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1554</v>
+        <v>0.1541</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.09616</v>
+        <v>-0.0953</v>
       </c>
       <c r="I6" t="n">
         <v>0.02282</v>
@@ -14055,22 +14055,22 @@
         <v>-0.76</v>
       </c>
       <c r="C7" t="n">
-        <v>2.202</v>
+        <v>2.182</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.962</v>
+        <v>-2.942</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7857</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1.039</v>
+        <v>1.029</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1111</v>
+        <v>0.1101</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2454</v>
+        <v>0.2432</v>
       </c>
       <c r="I7" t="n">
         <v>0.02092</v>
@@ -14096,22 +14096,22 @@
         <v>0.04</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8869</v>
+        <v>0.8793</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8469</v>
+        <v>-0.8393</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009185</v>
+        <v>0.009103999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9129</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1657</v>
+        <v>-0.1642</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0921</v>
+        <v>0.09128</v>
       </c>
       <c r="I8" t="n">
         <v>0.03835</v>
@@ -14137,22 +14137,22 @@
         <v>0.68</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.02394</v>
+        <v>-0.02371</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7039</v>
+        <v>0.7037</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.07621</v>
+        <v>-0.07554</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.05419</v>
+        <v>-0.05358</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1005</v>
+        <v>0.09966</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01947</v>
+        <v>0.0193</v>
       </c>
       <c r="I9" t="n">
         <v>-0.01355</v>
@@ -14178,22 +14178,22 @@
         <v>-1.14</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.5386</v>
+        <v>-0.5345</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6014</v>
+        <v>-0.6055</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2381</v>
+        <v>-0.236</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3402</v>
+        <v>-0.3367</v>
       </c>
       <c r="G10" t="n">
-        <v>0.124</v>
+        <v>0.1229</v>
       </c>
       <c r="H10" t="n">
-        <v>0.05053</v>
+        <v>0.05008</v>
       </c>
       <c r="I10" t="n">
         <v>-0.1349</v>
@@ -14219,28 +14219,28 @@
         <v>-7.7</v>
       </c>
       <c r="C11" t="n">
-        <v>-3.077</v>
+        <v>-3.063</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.623</v>
+        <v>-4.637</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.158</v>
+        <v>-1.148</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.699</v>
+        <v>-1.681</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01568</v>
+        <v>0.01554</v>
       </c>
       <c r="H11" t="n">
-        <v>0.04635</v>
+        <v>0.04593</v>
       </c>
       <c r="I11" t="n">
         <v>-0.03712</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2451</v>
+        <v>-0.259</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
@@ -14260,28 +14260,28 @@
         <v>-11.94</v>
       </c>
       <c r="C12" t="n">
-        <v>-4.847</v>
+        <v>-4.864</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.093</v>
+        <v>-7.076</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2155</v>
+        <v>-0.2136</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.463</v>
+        <v>-1.45</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04172</v>
+        <v>0.04135</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1661</v>
+        <v>0.1646</v>
       </c>
       <c r="I12" t="n">
         <v>0.07319000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.449</v>
+        <v>-3.48</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
@@ -14301,28 +14301,28 @@
         <v>-1.86</v>
       </c>
       <c r="C13" t="n">
-        <v>-4.763</v>
+        <v>-4.784</v>
       </c>
       <c r="D13" t="n">
-        <v>2.903</v>
+        <v>2.924</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2604</v>
+        <v>0.2581</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.03213</v>
+        <v>-0.03226</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2043</v>
+        <v>0.2024</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.02398</v>
+        <v>-0.02376</v>
       </c>
       <c r="I13" t="n">
         <v>-0.1028</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.069</v>
+        <v>-5.085</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -14342,22 +14342,22 @@
         <v>-1.28</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8763</v>
+        <v>0.8672</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.156</v>
+        <v>-2.147</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4272</v>
+        <v>0.4234</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6407</v>
+        <v>0.6344</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01013</v>
+        <v>0.01004</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1298</v>
+        <v>-0.1287</v>
       </c>
       <c r="I14" t="n">
         <v>-0.07196</v>
@@ -14383,22 +14383,22 @@
         <v>2.32</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1107</v>
+        <v>0.1098</v>
       </c>
       <c r="D15" t="n">
-        <v>2.209</v>
+        <v>2.21</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1748</v>
+        <v>-0.1732</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3926</v>
+        <v>0.3894</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1083</v>
+        <v>-0.1073</v>
       </c>
       <c r="H15" t="n">
-        <v>0.02401</v>
+        <v>0.0238</v>
       </c>
       <c r="I15" t="n">
         <v>-0.02282</v>
@@ -14424,22 +14424,22 @@
         <v>-3.98</v>
       </c>
       <c r="C16" t="n">
-        <v>-2.568</v>
+        <v>-2.545</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.412</v>
+        <v>-1.435</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5546</v>
+        <v>-0.5497</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8384</v>
+        <v>-0.8297</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1</v>
+        <v>-1.091</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01469</v>
+        <v>0.01456</v>
       </c>
       <c r="I16" t="n">
         <v>-0.0893</v>
@@ -14465,22 +14465,22 @@
         <v>6.82</v>
       </c>
       <c r="C17" t="n">
-        <v>1.63</v>
+        <v>1.613</v>
       </c>
       <c r="D17" t="n">
-        <v>5.19</v>
+        <v>5.207</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7175</v>
+        <v>0.7111</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.08384999999999999</v>
+        <v>-0.08455</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9832</v>
+        <v>0.9745</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1079</v>
+        <v>0.1069</v>
       </c>
       <c r="I17" t="n">
         <v>-0.09442</v>
@@ -14506,22 +14506,22 @@
         <v>6.5</v>
       </c>
       <c r="C18" t="n">
-        <v>2.549</v>
+        <v>2.524</v>
       </c>
       <c r="D18" t="n">
-        <v>3.951</v>
+        <v>3.976</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.7399</v>
       </c>
       <c r="F18" t="n">
-        <v>1.341</v>
+        <v>1.328</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2957</v>
+        <v>0.2931</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2632</v>
+        <v>0.2609</v>
       </c>
       <c r="I18" t="n">
         <v>-0.09805</v>
@@ -14547,22 +14547,22 @@
         <v>0.64</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1368</v>
+        <v>0.1365</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5032</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4578</v>
+        <v>-0.4537</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4178</v>
+        <v>0.4147</v>
       </c>
       <c r="G19" t="n">
-        <v>0.04768</v>
+        <v>0.04726</v>
       </c>
       <c r="H19" t="n">
-        <v>0.08958000000000001</v>
+        <v>0.08878</v>
       </c>
       <c r="I19" t="n">
         <v>0.03953</v>
@@ -14588,22 +14588,22 @@
         <v>2.14</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.6417</v>
+        <v>-0.6357</v>
       </c>
       <c r="D20" t="n">
-        <v>2.782</v>
+        <v>2.776</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.04891</v>
+        <v>-0.04847</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5464</v>
+        <v>-0.5414</v>
       </c>
       <c r="G20" t="n">
-        <v>0.03702</v>
+        <v>0.03669</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1012</v>
+        <v>-0.1003</v>
       </c>
       <c r="I20" t="n">
         <v>0.01778</v>
@@ -14629,22 +14629,22 @@
         <v>-2.16</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.8046</v>
+        <v>-0.7971</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.355</v>
+        <v>-1.363</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2825</v>
+        <v>-0.28</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3747</v>
+        <v>-0.3708</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.02233</v>
+        <v>-0.02213</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.09526999999999999</v>
+        <v>-0.09442</v>
       </c>
       <c r="I21" t="n">
         <v>-0.02976</v>
@@ -14673,7 +14673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14719,7 +14719,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -14739,19 +14739,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>İnflyasiyanın hədəf diapazonundan yuxarı olması: ehtimal 47%, skor 20 (P 4 × T 5, ölçü: inflyasiya)</t>
+          <t>İnflyasiyanın hədəf diapazonundan yuxarı olması: ehtimal 48%, skor 20 (P 4 × T 5, ölçü: inflyasiya)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -14776,14 +14776,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -14804,14 +14804,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -14832,14 +14832,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -14864,14 +14864,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -14896,14 +14896,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -14928,14 +14928,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -14960,14 +14960,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -14992,14 +14992,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -15024,14 +15024,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -15056,14 +15056,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -15079,19 +15079,19 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>minfin (Maliyyə Nazirliyi: təsdiq olunmuş büdcə göstəriciləri): son müşahidə 2025-01-01, 643 gün — köhnə; status: keş: şəbəkə yoxdur</t>
+          <t>minfin (Maliyyə Nazirliyi: təsdiq olunmuş büdcə göstəriciləri): son müşahidə 2025-01-01, 644 gün — köhnə; status: keş: şəbəkə yoxdur</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -15111,19 +15111,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Proqnoz qeyri-müəyyənliyi / model riski: model riski (P×T deyil): köhnəlməmiş konsensus (fr1, imf, mspec) ilə baza fərqi; köhnəlmiş xaric: bu60;caem;v8; hədd 0.5 f.b.; əlverişsiz fərq 1.04 f.b. (hədd 0.5 f.b.; alternativ paylanma FR2_model_risk.csv)</t>
+          <t>Proqnoz qeyri-müəyyənliyi / model riski: model riski (P×T deyil): köhnəlməmiş konsensus (fr1, imf, mspec) ilə baza fərqi; köhnəlmiş xaric: bu60;caem;v8; hədd 0.5 f.b.; əlverişsiz fərq 1.23 f.b. (hədd 0.5 f.b.; alternativ paylanma FR2_model_risk.csv)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -15139,19 +15139,19 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>dsk_macro: son müşahidə 2026-08-01 (66 gün)</t>
+          <t>brent: son müşahidə 2026-09-29 (8 gün)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -15167,19 +15167,19 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>dsk_cpi: son müşahidə 2026-08-01 (66 gün)</t>
+          <t>dsk_macro: son müşahidə 2026-08-01 (67 gün)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -15195,19 +15195,19 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>dsk_tables: son müşahidə 2026-04-01 (188 gün)</t>
+          <t>dsk_cpi: son müşahidə 2026-08-01 (67 gün)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -15223,19 +15223,19 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>minfin: son müşahidə 2026-03-01 (219 gün)</t>
+          <t>dsk_tables: son müşahidə 2026-04-01 (189 gün)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -15251,12 +15251,40 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>sofaz: son müşahidə 2026-06-30 (98 gün)</t>
+          <t>minfin: son müşahidə 2026-03-01 (220 gün)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>məlumat köhnəlib</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>aşağı</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>sofaz: son müşahidə 2026-06-30 (99 gün)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -15536,13 +15564,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4745</v>
+        <v>0.47525</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>3.668669484212645</v>
+        <v>3.670617789226606</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -15595,13 +15623,13 @@
         <v>0.4781</v>
       </c>
       <c r="F3" t="n">
-        <v>1.148235826232445</v>
+        <v>1.138379582543735</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.705239605565848</v>
+        <v>-2.69478577773629</v>
       </c>
       <c r="H3" t="n">
-        <v>0.243348499141978</v>
+        <v>0.2425556024249982</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
@@ -15648,10 +15676,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.141</v>
+        <v>0.1406</v>
       </c>
       <c r="F4" t="n">
-        <v>1.851448413476265</v>
+        <v>1.851298402304873</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -15707,13 +15735,13 @@
         <v>0.09805</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1865832516563455</v>
+        <v>0.1970342089263448</v>
       </c>
       <c r="G5" t="n">
         <v>4.098709226511697</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0.03566587654352295</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
@@ -15819,13 +15847,13 @@
         <v>0.2497</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5563236516274656</v>
+        <v>0.5511284474619335</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.170294823351427</v>
+        <v>-1.164559939744585</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1326579915023616</v>
+        <v>0.1269041995082851</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -15875,13 +15903,13 @@
         <v>0.14235</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6890986223274053</v>
+        <v>0.6829990166512481</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2345258142648071</v>
+        <v>-0.2276000371656484</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05433034510967913</v>
+        <v>0.05345996454349649</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -15984,7 +16012,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.0873</v>
+        <v>0.0963</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -15993,7 +16021,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6435914763817874</v>
+        <v>0.6387268468251253</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
@@ -16099,13 +16127,13 @@
         <v>0.089</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1961004415830367</v>
+        <v>0.1943394187931896</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.06713093437657885</v>
+        <v>-0.06512676188932408</v>
       </c>
       <c r="H12" t="n">
-        <v>0.03221603411784797</v>
+        <v>0.03198832797338956</v>
       </c>
       <c r="I12" t="n">
         <v>2</v>
@@ -16155,13 +16183,13 @@
         <v>0.4090909090909091</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1195370181539843</v>
+        <v>-0.1192364995457633</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0347866658476323</v>
+        <v>0.0344480214961637</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.00520413097235117</v>
+        <v>-0.00510986474365599</v>
       </c>
       <c r="I13" t="n">
         <v>4</v>
@@ -16267,13 +16295,13 @@
         <v>0.196</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08834150820121449</v>
+        <v>0.08868952185854784</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01274086849070601</v>
+        <v>0.01234050647732735</v>
       </c>
       <c r="H15" t="n">
-        <v>0.05368884380968081</v>
+        <v>0.05372688901177071</v>
       </c>
       <c r="I15" t="n">
         <v>3</v>
@@ -16547,7 +16575,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.040805</v>
+        <v>1.227415</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -17511,7 +17539,7 @@
         <v>2027</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4745</v>
+        <v>0.47525</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -17522,7 +17550,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>3.668669484212645</v>
+        <v>3.670617789226606</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -17565,12 +17593,12 @@
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -17615,13 +17643,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1.148235826232445</v>
+        <v>1.138379582543735</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.705239605565848</v>
+        <v>-2.69478577773629</v>
       </c>
       <c r="L3" t="n">
-        <v>0.243348499141978</v>
+        <v>0.2425556024249982</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -17629,10 +17657,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.2478071751588313</v>
+        <v>0.2438872251706225</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.597522879322406</v>
+        <v>-1.574552531783902</v>
       </c>
       <c r="P3" t="n">
         <v>4</v>
@@ -17652,7 +17680,7 @@
         <v>16</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5489715485217322</v>
+        <v>0.5442592784141596</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
@@ -17667,12 +17695,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -17709,7 +17737,7 @@
         <v>2027</v>
       </c>
       <c r="H4" t="n">
-        <v>0.141</v>
+        <v>0.1406</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -17717,7 +17745,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1.851448413476265</v>
+        <v>1.851298402304873</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -17750,7 +17778,7 @@
         <v>10</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2610542263001533</v>
+        <v>0.2602925553640652</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
@@ -17763,12 +17791,12 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -17813,13 +17841,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.1865832516563455</v>
+        <v>0.1970342089263448</v>
       </c>
       <c r="K5" t="n">
         <v>4.098709226511697</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0.03566587654352295</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -17827,10 +17855,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.004457327762490266</v>
+        <v>0.004696751119214867</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.02939096488047557</v>
+        <v>-0.03096193886336228</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
@@ -17850,7 +17878,7 @@
         <v>10</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01829448782490467</v>
+        <v>0.0193192041852281</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
@@ -17865,12 +17893,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -17929,10 +17957,10 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.02470259745759696</v>
+        <v>0.02466665617443659</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.10877395252808</v>
+        <v>-0.1081681072973538</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -17967,12 +17995,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -18017,13 +18045,13 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.5563236516274656</v>
+        <v>0.5511284474619335</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.170294823351427</v>
+        <v>-1.164559939744585</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1326579915023616</v>
+        <v>0.1269041995082851</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -18050,7 +18078,7 @@
         <v>9</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1389140158113782</v>
+        <v>0.1376167733312448</v>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
@@ -18063,12 +18091,12 @@
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -18113,13 +18141,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.6890986223274053</v>
+        <v>0.6829990166512481</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2345258142648071</v>
+        <v>-0.2276000371656484</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05433034510967913</v>
+        <v>0.05345996454349649</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -18127,10 +18155,10 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.04282989095060522</v>
+        <v>0.04211715012169798</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2618013632008695</v>
+        <v>-0.258144802839415</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
@@ -18150,7 +18178,7 @@
         <v>6</v>
       </c>
       <c r="U8" t="n">
-        <v>0.09809318888830615</v>
+        <v>0.09722491002030517</v>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
@@ -18165,12 +18193,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -18229,7 +18257,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.002504796418820543</v>
+        <v>0.002505313750568683</v>
       </c>
       <c r="O9" t="n">
         <v>-0.01906</v>
@@ -18267,12 +18295,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -18309,7 +18337,7 @@
         <v>2027</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0873</v>
+        <v>0.0963</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -18323,7 +18351,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6435914763817874</v>
+        <v>0.6387268468251253</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -18363,12 +18391,12 @@
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -18427,10 +18455,10 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.001584408462701837</v>
+        <v>0.001585879879853311</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.007395369314715937</v>
+        <v>-0.007480373559712671</v>
       </c>
       <c r="P11" t="n">
         <v>4</v>
@@ -18465,12 +18493,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -18515,13 +18543,13 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.1961004415830367</v>
+        <v>0.1943394187931896</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.06713093437657885</v>
+        <v>-0.06512676188932408</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03221603411784797</v>
+        <v>0.03198832797338956</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -18529,10 +18557,10 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0.0003427505298066262</v>
+        <v>0.0003229841702029119</v>
       </c>
       <c r="O12" t="n">
-        <v>0.006396235249584953</v>
+        <v>0.006421466419337344</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
@@ -18552,7 +18580,7 @@
         <v>4</v>
       </c>
       <c r="U12" t="n">
-        <v>0.01745293930089026</v>
+        <v>0.01729620827259387</v>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
@@ -18567,12 +18595,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -18617,13 +18645,13 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-0.1195370181539843</v>
+        <v>-0.1192364995457633</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0347866658476323</v>
+        <v>0.0344480214961637</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.00520413097235117</v>
+        <v>-0.00510986474365599</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -18631,10 +18659,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.01330480899020586</v>
+        <v>0.0131902282566472</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.06706297589430205</v>
+        <v>-0.06682261689820221</v>
       </c>
       <c r="P13" t="n">
         <v>4</v>
@@ -18669,12 +18697,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -18771,12 +18799,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -18821,13 +18849,13 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.08834150820121449</v>
+        <v>0.08868952185854784</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01274086849070601</v>
+        <v>0.01234050647732735</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05368884380968081</v>
+        <v>0.05372688901177071</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -18835,10 +18863,10 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0.00227452952368823</v>
+        <v>0.002292002753467837</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0233904727164868</v>
+        <v>-0.02348752982738298</v>
       </c>
       <c r="P15" t="n">
         <v>3</v>
@@ -18858,7 +18886,7 @@
         <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>0.01731493560743804</v>
+        <v>0.01738314628427538</v>
       </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
@@ -18873,12 +18901,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -18937,10 +18965,10 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0.0006736773439720752</v>
+        <v>0.0006746846239985678</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0007571153807486505</v>
+        <v>-0.0007614685875397473</v>
       </c>
       <c r="P16" t="n">
         <v>3</v>
@@ -18975,12 +19003,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -19039,7 +19067,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.878673933708213e-05</v>
+        <v>4.879603129663849e-05</v>
       </c>
       <c r="O17" t="n">
         <v>-6.762636662501582e-06</v>
@@ -19077,12 +19105,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -19141,10 +19169,10 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0.0001592894519315203</v>
+        <v>0.0001588549032787294</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0004799999999999998</v>
+        <v>-0.0005300000000000001</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
@@ -19179,12 +19207,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -19281,12 +19309,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -19331,7 +19359,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1.040805</v>
+        <v>1.227415</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -19367,7 +19395,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.040805</v>
+        <v>-1.227415</v>
       </c>
       <c r="W20" t="n">
         <v>-0.6416000000000004</v>
@@ -19383,12 +19411,12 @@
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -19403,7 +19431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19412,16 +19440,19 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19505,11 +19536,26 @@
           <t>ES10</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>merkez</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>musahide_payi</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>baza_izah</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -19539,37 +19585,48 @@
         <v>5.312</v>
       </c>
       <c r="H2" t="n">
-        <v>1.479390236951072</v>
+        <v>1.482919585826119</v>
       </c>
       <c r="I2" t="n">
-        <v>1.926060899014274</v>
+        <v>1.927049212179706</v>
       </c>
       <c r="J2" t="n">
-        <v>2.538446215225452</v>
+        <v>2.54057171921383</v>
       </c>
       <c r="K2" t="n">
         <v>3.170666666666667</v>
       </c>
       <c r="L2" t="n">
-        <v>3.792409202823086</v>
+        <v>3.793008456036261</v>
       </c>
       <c r="M2" t="n">
-        <v>4.394027663072614</v>
+        <v>4.395585603340777</v>
       </c>
       <c r="N2" t="n">
-        <v>4.827534615649488</v>
+        <v>4.827943328473756</v>
       </c>
       <c r="O2" t="n">
-        <v>3.16328396444787</v>
+        <v>3.164025707033471</v>
       </c>
       <c r="P2" t="n">
-        <v>1.292738136498327</v>
+        <v>1.293440917461872</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.170666666666667</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz (YTD məlumatından əvvəl) — zolaq il-əvvəlindən faktiki ilə şərtləndirilib, 'baza' zolaqdan kənar ola bilər; mərkəz = 'merkez'</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -19599,37 +19656,46 @@
         <v>5.43</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1067028474052741</v>
+        <v>0.1062501683316305</v>
       </c>
       <c r="I3" t="n">
-        <v>1.331371404281145</v>
+        <v>1.341279800851993</v>
       </c>
       <c r="J3" t="n">
-        <v>3.317802945026939</v>
+        <v>3.320000301522238</v>
       </c>
       <c r="K3" t="n">
         <v>5.43</v>
       </c>
       <c r="L3" t="n">
-        <v>7.404707297752129</v>
+        <v>7.403436654495416</v>
       </c>
       <c r="M3" t="n">
-        <v>9.173450133608767</v>
+        <v>9.173443840642033</v>
       </c>
       <c r="N3" t="n">
-        <v>10.35643436933132</v>
+        <v>10.35568918777159</v>
       </c>
       <c r="O3" t="n">
-        <v>5.333419234430722</v>
+        <v>5.336756323098694</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.477971036994372</v>
+        <v>-0.4731835153133596</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -19659,37 +19725,46 @@
         <v>5.603</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4191556007638805</v>
+        <v>0.4221504052966534</v>
       </c>
       <c r="I4" t="n">
-        <v>1.634943532042462</v>
+        <v>1.631048315123231</v>
       </c>
       <c r="J4" t="n">
-        <v>3.567726859973746</v>
+        <v>3.568332825490241</v>
       </c>
       <c r="K4" t="n">
         <v>5.603</v>
       </c>
       <c r="L4" t="n">
-        <v>7.50706917787449</v>
+        <v>7.508457882268849</v>
       </c>
       <c r="M4" t="n">
-        <v>9.173188334985447</v>
+        <v>9.17452620255489</v>
       </c>
       <c r="N4" t="n">
-        <v>10.18570640933398</v>
+        <v>10.18663926359327</v>
       </c>
       <c r="O4" t="n">
-        <v>5.480376577858427</v>
+        <v>5.482972804281894</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.04564397416378312</v>
+        <v>-0.04256064131559055</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.603</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -19719,37 +19794,46 @@
         <v>5.632</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8309198099560298</v>
+        <v>0.8310607200389457</v>
       </c>
       <c r="I5" t="n">
-        <v>1.919410032966553</v>
+        <v>1.916564145660423</v>
       </c>
       <c r="J5" t="n">
-        <v>3.721615646788521</v>
+        <v>3.721503035761458</v>
       </c>
       <c r="K5" t="n">
         <v>5.632</v>
       </c>
       <c r="L5" t="n">
-        <v>7.544161924421059</v>
+        <v>7.548216225760745</v>
       </c>
       <c r="M5" t="n">
-        <v>9.280858125945068</v>
+        <v>9.280372433292248</v>
       </c>
       <c r="N5" t="n">
-        <v>10.34780917111653</v>
+        <v>10.33990206251179</v>
       </c>
       <c r="O5" t="n">
-        <v>5.625503652057341</v>
+        <v>5.626081589489022</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3929013720046147</v>
+        <v>0.3921986772309005</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5.632</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -19779,37 +19863,46 @@
         <v>5.727</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5221845551192122</v>
+        <v>0.5173721180203936</v>
       </c>
       <c r="I6" t="n">
-        <v>1.700749434169665</v>
+        <v>1.694868082544648</v>
       </c>
       <c r="J6" t="n">
-        <v>3.638132160596808</v>
+        <v>3.638307689594504</v>
       </c>
       <c r="K6" t="n">
         <v>5.727</v>
       </c>
       <c r="L6" t="n">
-        <v>7.738480853658364</v>
+        <v>7.732833225187159</v>
       </c>
       <c r="M6" t="n">
-        <v>9.580007378735891</v>
+        <v>9.572082567155261</v>
       </c>
       <c r="N6" t="n">
-        <v>10.79158639238588</v>
+        <v>10.7825480174524</v>
       </c>
       <c r="O6" t="n">
-        <v>5.700363947862166</v>
+        <v>5.698475535736769</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1064796567137457</v>
+        <v>0.1041524640379338</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5.727</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -19839,37 +19932,48 @@
         <v>5.2991</v>
       </c>
       <c r="H7" t="n">
-        <v>3.760282406733691</v>
+        <v>3.760569233365816</v>
       </c>
       <c r="I7" t="n">
-        <v>4.077459164102876</v>
+        <v>4.078374868310719</v>
       </c>
       <c r="J7" t="n">
-        <v>4.689121564536991</v>
+        <v>4.68942674458736</v>
       </c>
       <c r="K7" t="n">
-        <v>5.566366666694572</v>
+        <v>5.566366666685266</v>
       </c>
       <c r="L7" t="n">
-        <v>6.588035442365568</v>
+        <v>6.58791243007648</v>
       </c>
       <c r="M7" t="n">
-        <v>7.566538565662351</v>
+        <v>7.565248813366443</v>
       </c>
       <c r="N7" t="n">
-        <v>8.163748751908782</v>
+        <v>8.163205352616226</v>
       </c>
       <c r="O7" t="n">
-        <v>5.717944572648214</v>
+        <v>5.718363288921971</v>
       </c>
       <c r="P7" t="n">
-        <v>8.390210289955695</v>
+        <v>8.391732288853827</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5.566366666666667</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz (YTD məlumatından əvvəl) — zolaq il-əvvəlindən faktiki ilə şərtləndirilib, 'baza' zolaqdan kənar ola bilər; mərkəz = 'merkez'</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -19899,37 +20003,46 @@
         <v>5.7416</v>
       </c>
       <c r="H8" t="n">
-        <v>1.637477394349494</v>
+        <v>1.645148908227121</v>
       </c>
       <c r="I8" t="n">
-        <v>2.179166203517428</v>
+        <v>2.184412050944329</v>
       </c>
       <c r="J8" t="n">
-        <v>3.494476696426859</v>
+        <v>3.500331262452311</v>
       </c>
       <c r="K8" t="n">
-        <v>5.741600027738388</v>
+        <v>5.741600000291456</v>
       </c>
       <c r="L8" t="n">
-        <v>8.60589912781338</v>
+        <v>8.606442771643604</v>
       </c>
       <c r="M8" t="n">
-        <v>11.71908775101037</v>
+        <v>11.72568071011577</v>
       </c>
       <c r="N8" t="n">
-        <v>13.71291149828101</v>
+        <v>13.73922647261201</v>
       </c>
       <c r="O8" t="n">
-        <v>6.47497930882246</v>
+        <v>6.481210665183514</v>
       </c>
       <c r="P8" t="n">
-        <v>14.73518651597717</v>
+        <v>14.75665689404205</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5.7416</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -19959,37 +20072,46 @@
         <v>5.8752</v>
       </c>
       <c r="H9" t="n">
-        <v>1.733983414456829</v>
+        <v>1.735739831562084</v>
       </c>
       <c r="I9" t="n">
-        <v>2.242613542393661</v>
+        <v>2.245603069040152</v>
       </c>
       <c r="J9" t="n">
-        <v>3.491395674993615</v>
+        <v>3.492039412925971</v>
       </c>
       <c r="K9" t="n">
-        <v>5.875200000046539</v>
+        <v>5.875200005261181</v>
       </c>
       <c r="L9" t="n">
-        <v>8.936728145768434</v>
+        <v>8.926048374258578</v>
       </c>
       <c r="M9" t="n">
-        <v>11.9173179351248</v>
+        <v>11.91879376830065</v>
       </c>
       <c r="N9" t="n">
-        <v>13.97630078261479</v>
+        <v>13.97195313384571</v>
       </c>
       <c r="O9" t="n">
-        <v>6.590327683895815</v>
+        <v>6.589027594007982</v>
       </c>
       <c r="P9" t="n">
-        <v>14.62990256135773</v>
+        <v>14.64314152272278</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.8752</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -20019,37 +20141,46 @@
         <v>5.9149</v>
       </c>
       <c r="H10" t="n">
-        <v>1.704941587710936</v>
+        <v>1.707591500771425</v>
       </c>
       <c r="I10" t="n">
-        <v>2.244794195067345</v>
+        <v>2.245034568830815</v>
       </c>
       <c r="J10" t="n">
-        <v>3.490040498346176</v>
+        <v>3.490739779339362</v>
       </c>
       <c r="K10" t="n">
-        <v>5.914900000943524</v>
+        <v>5.914900007656625</v>
       </c>
       <c r="L10" t="n">
-        <v>9.012587800750067</v>
+        <v>9.005541012869669</v>
       </c>
       <c r="M10" t="n">
-        <v>11.9316606799955</v>
+        <v>11.93322066880248</v>
       </c>
       <c r="N10" t="n">
-        <v>13.96198756898125</v>
+        <v>13.96279584891859</v>
       </c>
       <c r="O10" t="n">
-        <v>6.630014971426371</v>
+        <v>6.627810625691341</v>
       </c>
       <c r="P10" t="n">
-        <v>14.68812453807412</v>
+        <v>14.70047384137512</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.9149</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -20079,37 +20210,46 @@
         <v>5.9278</v>
       </c>
       <c r="H11" t="n">
-        <v>1.675902225958274</v>
+        <v>1.683341084588279</v>
       </c>
       <c r="I11" t="n">
-        <v>2.234868544537479</v>
+        <v>2.240520701191821</v>
       </c>
       <c r="J11" t="n">
-        <v>3.49385732630189</v>
+        <v>3.498508714377382</v>
       </c>
       <c r="K11" t="n">
-        <v>5.927800000663005</v>
+        <v>5.927800000000158</v>
       </c>
       <c r="L11" t="n">
-        <v>8.971672293188059</v>
+        <v>8.974762144347174</v>
       </c>
       <c r="M11" t="n">
-        <v>11.91142226283644</v>
+        <v>11.90764014977851</v>
       </c>
       <c r="N11" t="n">
-        <v>13.88788660227985</v>
+        <v>13.90235858631616</v>
       </c>
       <c r="O11" t="n">
-        <v>6.610022289955002</v>
+        <v>6.615220332612924</v>
       </c>
       <c r="P11" t="n">
-        <v>14.69650881741985</v>
+        <v>14.71867533053414</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.9278</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -20136,40 +20276,49 @@
         <v>2026</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6555590944366291</v>
+        <v>0.6554658813054888</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00657473344228604</v>
+        <v>0.08824255608521883</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1760716122959948</v>
+        <v>0.2341828241343352</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4150116234452855</v>
+        <v>0.4432499604269328</v>
       </c>
       <c r="K12" t="n">
-        <v>0.655559094436629</v>
+        <v>0.6554658813054888</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8888141223841095</v>
+        <v>0.8614771236611602</v>
       </c>
       <c r="M12" t="n">
-        <v>1.133869085605758</v>
+        <v>1.073810541648831</v>
       </c>
       <c r="N12" t="n">
-        <v>1.295369682453975</v>
+        <v>1.214802859320826</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6534726342017219</v>
+        <v>0.6530976648879688</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.07912354178002338</v>
+        <v>0.01173244678452152</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.6554658813054888</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -20196,40 +20345,49 @@
         <v>2027</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3211499702600046</v>
+        <v>0.261382610808425</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.334760832383269</v>
+        <v>-1.397596468393155</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9176766394598171</v>
+        <v>-0.9717758105434385</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2962402195587849</v>
+        <v>-0.3546230156981584</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3211499702600047</v>
+        <v>0.2613826108084251</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9292641368249409</v>
+        <v>0.8694696668639241</v>
       </c>
       <c r="M13" t="n">
-        <v>1.538995514648556</v>
+        <v>1.482136534365544</v>
       </c>
       <c r="N13" t="n">
-        <v>1.988296533602897</v>
+        <v>1.928779064888093</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3185650950058835</v>
+        <v>0.2594461915601023</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.556464033870177</v>
+        <v>-1.61452635608433</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.261382610808425</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -20256,40 +20414,49 @@
         <v>2028</v>
       </c>
       <c r="G14" t="n">
-        <v>0.03352826722117876</v>
+        <v>-0.06153457657170647</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.657514945386926</v>
+        <v>-1.684087837188643</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.231311453837113</v>
+        <v>-1.269894783986019</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5992334562083241</v>
+        <v>-0.6677589888267532</v>
       </c>
       <c r="K14" t="n">
-        <v>0.03352826722117874</v>
+        <v>-0.06153457657170645</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6549992855624015</v>
+        <v>0.5393175143445756</v>
       </c>
       <c r="M14" t="n">
-        <v>1.271751405256316</v>
+        <v>1.125635961797465</v>
       </c>
       <c r="N14" t="n">
-        <v>1.682377415638985</v>
+        <v>1.514114526446256</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0189304929111973</v>
+        <v>-0.07353629004657494</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.903890925874671</v>
+        <v>-1.912219893315046</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.06153457657170647</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -20316,40 +20483,49 @@
         <v>2029</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1088130080298695</v>
+        <v>-0.005875529708835879</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.317431945226393</v>
+        <v>-1.468942068539869</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9335235506643019</v>
+        <v>-1.088422756825059</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4164503014780412</v>
+        <v>-0.5482938729331017</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1088130080298695</v>
+        <v>-0.005875529708835865</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6524612510560888</v>
+        <v>0.5507804708238435</v>
       </c>
       <c r="M15" t="n">
-        <v>1.226806253622443</v>
+        <v>1.130737438200285</v>
       </c>
       <c r="N15" t="n">
-        <v>1.625823997066389</v>
+        <v>1.541669947926916</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1187066115217841</v>
+        <v>0.001491646661877367</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.549855535006234</v>
+        <v>-1.708316883361015</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.005875529708835879</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -20376,40 +20552,49 @@
         <v>2030</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1410542320997969</v>
+        <v>0.01289378240004166</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.821142189161026</v>
+        <v>-1.704778637450248</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.293837440329985</v>
+        <v>-1.24710057324276</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5717717033029435</v>
+        <v>-0.6161099576621863</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1410542320997969</v>
+        <v>0.01289378240004166</v>
       </c>
       <c r="L16" t="n">
-        <v>0.864618461963761</v>
+        <v>0.6563658971302642</v>
       </c>
       <c r="M16" t="n">
-        <v>1.603262895663663</v>
+        <v>1.314927425243175</v>
       </c>
       <c r="N16" t="n">
-        <v>2.136078990947605</v>
+        <v>1.784981195629086</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1443927958620436</v>
+        <v>0.01882848513537284</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.088404340307621</v>
+        <v>-1.949157154165313</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.01289378240004166</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -20465,11 +20650,22 @@
       <c r="P17" t="n">
         <v>72.81431481156208</v>
       </c>
+      <c r="Q17" t="n">
+        <v>87.01530585106383</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz (YTD məlumatından əvvəl) — zolaq il-əvvəlindən faktiki ilə şərtləndirilib, 'baza' zolaqdan kənar ola bilər; mərkəz = 'merkez'</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -20525,11 +20721,20 @@
       <c r="P18" t="n">
         <v>32.81283920115138</v>
       </c>
+      <c r="Q18" t="n">
+        <v>68.97</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -20585,11 +20790,20 @@
       <c r="P19" t="n">
         <v>26.4483703255685</v>
       </c>
+      <c r="Q19" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -20645,11 +20859,20 @@
       <c r="P20" t="n">
         <v>22.27847021505278</v>
       </c>
+      <c r="Q20" t="n">
+        <v>69.45999999999999</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -20704,6 +20927,15 @@
       </c>
       <c r="P21" t="n">
         <v>18.88553936441177</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>69.19</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>rəsmi proqnoz</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -20791,16 +21023,16 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.02472288999762812</v>
+        <v>0.02857604243653894</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6593744371216778</v>
+        <v>0.6639171298514432</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.675501153189637</v>
+        <v>-3.695793636253052</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.700224043187265</v>
+        <v>-3.724369678689591</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -20828,16 +21060,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.3275635360247027</v>
+        <v>0.324928965755358</v>
       </c>
       <c r="E3" t="n">
-        <v>0.131465228447678</v>
+        <v>0.1291193882140458</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5929085455230289</v>
+        <v>-0.5797350535884014</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9204720815477316</v>
+        <v>-0.9046640193437594</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -20865,16 +21097,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.3383380143498017</v>
+        <v>-0.3352252948146286</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1163419467111533</v>
+        <v>0.1147678369565764</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.015388812124477</v>
+        <v>-1.005113807254771</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6770507977746748</v>
+        <v>-0.6698885124401424</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -20902,16 +21134,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.0007267323018947144</v>
+        <v>-0.0007199093868363993</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04282989095060522</v>
+        <v>0.04211715012169798</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2625280955027642</v>
+        <v>-0.2588647122262514</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2618013632008695</v>
+        <v>-0.258144802839415</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -20942,13 +21174,13 @@
         <v>-0.06663063267295084</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02470259745759696</v>
+        <v>0.02466665617443659</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1754045852010308</v>
+        <v>-0.1747987399703046</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.10877395252808</v>
+        <v>-0.1081681072973538</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -20976,16 +21208,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.009633218001585002</v>
+        <v>-0.009637997468117167</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01330480899020586</v>
+        <v>0.0131902282566472</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.07669619389588705</v>
+        <v>-0.07646061436631937</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.06706297589430205</v>
+        <v>-0.06682261689820221</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -21013,16 +21245,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.02028326162747899</v>
+        <v>-0.02141937378483076</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004457327762490266</v>
+        <v>0.004696751119214867</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.04967422650795456</v>
+        <v>-0.05238131264819303</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.02939096488047557</v>
+        <v>-0.03096193886336228</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -21050,16 +21282,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01735177720068385</v>
+        <v>-0.01746443435885749</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00227452952368823</v>
+        <v>0.002292002753467837</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.04074224991717065</v>
+        <v>-0.04095196418624047</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0233904727164868</v>
+        <v>-0.02348752982738298</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -21090,7 +21322,7 @@
         <v>0.00106</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002504796418820543</v>
+        <v>0.002505313750568683</v>
       </c>
       <c r="F10" t="n">
         <v>-0.018</v>
@@ -21127,13 +21359,13 @@
         <v>8.500424499673507e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001584408462701837</v>
+        <v>0.001585879879853311</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.007310365069719202</v>
+        <v>-0.007395369314715936</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.007395369314715937</v>
+        <v>-0.007480373559712671</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -21161,16 +21393,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.02529804488116331</v>
+        <v>-0.02504787432268279</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.44759116647816e-05</v>
+        <v>-6.365680672841569e-05</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.02721865249383047</v>
+        <v>-0.02706336817094981</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.001920607612667154</v>
+        <v>-0.002015493848267016</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -21201,13 +21433,13 @@
         <v>0.02865427509001219</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0006736773439720752</v>
+        <v>0.0006746846239985678</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02789715970926353</v>
+        <v>0.02789280650247244</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0007571153807486505</v>
+        <v>-0.0007614685875397473</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -21238,13 +21470,13 @@
         <v>-0.00017</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0001592894519315203</v>
+        <v>0.0001588549032787294</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0006499999999999999</v>
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0004799999999999998</v>
+        <v>-0.0005300000000000001</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -21275,7 +21507,7 @@
         <v>0.000209641736537549</v>
       </c>
       <c r="E15" t="n">
-        <v>4.878673933708213e-05</v>
+        <v>4.879603129663849e-05</v>
       </c>
       <c r="F15" t="n">
         <v>0.0002028790998750474</v>
@@ -21309,16 +21541,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.0004444316275964654</v>
+        <v>-0.0004420893558450627</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0003427505298066262</v>
+        <v>0.0003229841702029119</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005951803621988487</v>
+        <v>0.005979377063492282</v>
       </c>
       <c r="G16" t="n">
-        <v>0.006396235249584953</v>
+        <v>0.006421466419337344</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
